--- a/output/2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx
@@ -474,7 +474,6 @@
           <t>Industrijska oprema (Tehnoloska resenja za industrijski vazduh)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Beograd (Zemun) - Grad Beograd</t>
@@ -490,10 +489,9 @@
           <t>011/3077-086</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Confermato su directory PlanPlus (indirizzo Banatska 28V, Zemun). Categoria esplicita coerente col settore. Sito web ufficiale non identificato, email non reperita.</t>
+          <t>Confermato su directory PlanPlus (indirizzo Banatska 28V, Zemun). Categoria esplicita coerente col settore. Sito web ufficiale non identificato, email non reperita. [DUPLICATO — vedi anche: 2026-10-06_21_Serbia_Grad_Beograd_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -592,7 +590,6 @@
           <t>BSM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Beograd (Savski Venac, Bulevar vojvode Misica 14) - Grad Beograd</t>
@@ -608,7 +605,6 @@
           <t>011/655-5570</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermato su PlanPlus (categoria: manutenzione/pulizia edifici). Rischio che sia erogatore di servizi di pulizia (uso proprio macchine) piu' che distributore B2B puro. Prodotto adiacente ma diverso da impianti fissi di aspirazione polveri/trucioli/fumi.</t>

--- a/output/2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-06_22_Serbia_Grad_Beograd_Impiantistica_aspirazione_industriale.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
